--- a/IONQ.xlsx
+++ b/IONQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C68CEA7-62C9-44AE-93B0-22E3F5F6C0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD0889A-5596-49A4-9D1F-268E5D2241AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="4500" windowWidth="23600" windowHeight="13830" activeTab="1" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
+    <workbookView xWindow="9870" yWindow="3540" windowWidth="19050" windowHeight="16100" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -65,6 +65,7 @@
     <author>tc={A6E9DABB-1376-4112-A26B-944B948407A8}</author>
     <author>tc={C126CAEF-E2E0-4E27-89FF-07FBEE96CB7E}</author>
     <author>tc={52746AA8-06E3-4D64-87ED-D1AB9D96C22E}</author>
+    <author>tc={A42B0B24-99E3-44AD-B080-B1580405B567}</author>
   </authors>
   <commentList>
     <comment ref="Q5" authorId="0" shapeId="0" xr:uid="{5F4D892F-8EE7-4A57-8773-FC47BA737F6C}">
@@ -273,6 +274,14 @@
 48m from acquisitions</t>
       </text>
     </comment>
+    <comment ref="AJ30" authorId="23" shapeId="0" xr:uid="{A42B0B24-99E3-44AD-B080-B1580405B567}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q1: 260-270m</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -874,7 +883,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -910,6 +919,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -932,7 +947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -979,10 +994,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1057,16 +1068,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>39120</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>50163</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>3969</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>39120</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>50163</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>85611</xdr:rowOff>
+      <xdr:rowOff>81642</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1081,8 +1092,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21787870" y="3969"/>
-          <a:ext cx="0" cy="9328830"/>
+          <a:off x="22429772" y="0"/>
+          <a:ext cx="0" cy="10357599"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1571,6 +1582,9 @@
 18.8m from ID quantique
 48m from acquisitions</text>
   </threadedComment>
+  <threadedComment ref="AJ30" dT="2026-07-27T13:56:14.43" personId="{8FE8731E-1419-4CF8-BDB7-325E36ECD730}" id="{A42B0B24-99E3-44AD-B080-B1580405B567}">
+    <text>Q1: 260-270m</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1594,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>31.53</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1"/>
       <c r="Q2" s="1"/>
@@ -1608,10 +1622,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="4">
-        <v>368.98291699999999</v>
+        <v>371</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="N3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1626,7 +1640,7 @@
       </c>
       <c r="J4" s="4">
         <f>+J2*J3</f>
-        <v>11634.031373010001</v>
+        <v>13727</v>
       </c>
       <c r="N4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1640,11 +1654,11 @@
         <v>3</v>
       </c>
       <c r="J5" s="4">
-        <f>1030.865+1361.291+944.643</f>
-        <v>3336.799</v>
+        <f>493.538+1539.932+1058.426</f>
+        <v>3091.8959999999997</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="N5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1658,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="13" x14ac:dyDescent="0.3">
@@ -1670,7 +1684,7 @@
       </c>
       <c r="J7" s="4">
         <f>+J4-J5+J6</f>
-        <v>8297.2323730099997</v>
+        <v>10635.103999999999</v>
       </c>
       <c r="N7" s="4"/>
       <c r="Q7" s="4"/>
@@ -3035,11 +3049,11 @@
       </c>
       <c r="S17" s="22">
         <f>+SUM(T30:AB30)-S20</f>
-        <v>323.69600000000003</v>
+        <v>382.49599999999998</v>
       </c>
       <c r="T17" s="22">
         <f>+SUM(U30:AC30)-T20</f>
-        <v>270.80599999999998</v>
+        <v>329.60599999999999</v>
       </c>
       <c r="AF17" s="23"/>
       <c r="AH17" s="23"/>
@@ -3625,19 +3639,19 @@
         <v>61.89</v>
       </c>
       <c r="W30" s="13">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="X30" s="13">
         <f>+W30+5</f>
-        <v>55</v>
+        <v>69.7</v>
       </c>
       <c r="Y30" s="13">
         <f>+X30+5</f>
-        <v>60</v>
+        <v>74.7</v>
       </c>
       <c r="Z30" s="13">
         <f>+Y30+5</f>
-        <v>65</v>
+        <v>79.7</v>
       </c>
       <c r="AC30" s="13">
         <v>0.2</v>
@@ -3663,304 +3677,304 @@
         <v>130.02249999999998</v>
       </c>
       <c r="AJ30" s="13">
-        <f>+AI30*1.9</f>
-        <v>247.04274999999996</v>
+        <f>SUM(W30:Z30)</f>
+        <v>288.8</v>
       </c>
       <c r="AK30" s="13">
         <f>+AJ30*1.9</f>
-        <v>469.38122499999992</v>
+        <v>548.72</v>
       </c>
       <c r="AL30" s="13">
         <f>+AK30*1.9</f>
-        <v>891.82432749999975</v>
+        <v>1042.568</v>
       </c>
       <c r="AM30" s="13">
         <f>+AL30*1.9</f>
-        <v>1694.4662222499994</v>
+        <v>1980.8791999999999</v>
       </c>
       <c r="AN30" s="13">
         <f>+AM30*1.1</f>
-        <v>1863.9128444749995</v>
+        <v>2178.9671199999998</v>
       </c>
       <c r="AO30" s="13">
         <f t="shared" ref="AO30:AS30" si="12">+AN30*1.1</f>
-        <v>2050.3041289224998</v>
+        <v>2396.863832</v>
       </c>
       <c r="AP30" s="13">
         <f t="shared" si="12"/>
-        <v>2255.3345418147501</v>
+        <v>2636.5502152000004</v>
       </c>
       <c r="AQ30" s="13">
         <f t="shared" si="12"/>
-        <v>2480.8679959962251</v>
+        <v>2900.2052367200008</v>
       </c>
       <c r="AR30" s="13">
         <f t="shared" si="12"/>
-        <v>2728.9547955958478</v>
+        <v>3190.2257603920011</v>
       </c>
       <c r="AS30" s="13">
         <f t="shared" si="12"/>
-        <v>3001.8502751554329</v>
+        <v>3509.2483364312016</v>
       </c>
       <c r="AT30" s="13">
         <f>+AS30*1.1</f>
-        <v>3302.0353026709763</v>
+        <v>3860.1731700743221</v>
       </c>
       <c r="AU30" s="13">
         <f t="shared" ref="AU30:DF30" si="13">+AT30*1.1</f>
-        <v>3632.2388329380742</v>
+        <v>4246.1904870817543</v>
       </c>
       <c r="AV30" s="13">
         <f t="shared" si="13"/>
-        <v>3995.462716231882</v>
+        <v>4670.8095357899301</v>
       </c>
       <c r="AW30" s="13">
         <f t="shared" si="13"/>
-        <v>4395.0089878550707</v>
+        <v>5137.8904893689232</v>
       </c>
       <c r="AX30" s="13">
         <f t="shared" si="13"/>
-        <v>4834.5098866405779</v>
+        <v>5651.6795383058161</v>
       </c>
       <c r="AY30" s="13">
         <f t="shared" si="13"/>
-        <v>5317.9608753046359</v>
+        <v>6216.8474921363986</v>
       </c>
       <c r="AZ30" s="13">
         <f t="shared" si="13"/>
-        <v>5849.7569628351002</v>
+        <v>6838.5322413500389</v>
       </c>
       <c r="BA30" s="13">
         <f t="shared" si="13"/>
-        <v>6434.7326591186111</v>
+        <v>7522.3854654850438</v>
       </c>
       <c r="BB30" s="13">
         <f t="shared" si="13"/>
-        <v>7078.2059250304728</v>
+        <v>8274.6240120335497</v>
       </c>
       <c r="BC30" s="13">
         <f t="shared" si="13"/>
-        <v>7786.0265175335207</v>
+        <v>9102.0864132369061</v>
       </c>
       <c r="BD30" s="13">
         <f t="shared" si="13"/>
-        <v>8564.6291692868726</v>
+        <v>10012.295054560598</v>
       </c>
       <c r="BE30" s="13">
         <f t="shared" si="13"/>
-        <v>9421.0920862155599</v>
+        <v>11013.524560016658</v>
       </c>
       <c r="BF30" s="13">
         <f t="shared" si="13"/>
-        <v>10363.201294837118</v>
+        <v>12114.877016018325</v>
       </c>
       <c r="BG30" s="13">
         <f t="shared" si="13"/>
-        <v>11399.52142432083</v>
+        <v>13326.364717620158</v>
       </c>
       <c r="BH30" s="13">
         <f t="shared" si="13"/>
-        <v>12539.473566752915</v>
+        <v>14659.001189382174</v>
       </c>
       <c r="BI30" s="13">
         <f t="shared" si="13"/>
-        <v>13793.420923428208</v>
+        <v>16124.901308320392</v>
       </c>
       <c r="BJ30" s="13">
         <f t="shared" si="13"/>
-        <v>15172.76301577103</v>
+        <v>17737.391439152434</v>
       </c>
       <c r="BK30" s="13">
         <f t="shared" si="13"/>
-        <v>16690.039317348135</v>
+        <v>19511.130583067679</v>
       </c>
       <c r="BL30" s="13">
         <f t="shared" si="13"/>
-        <v>18359.043249082952</v>
+        <v>21462.243641374447</v>
       </c>
       <c r="BM30" s="13">
         <f t="shared" si="13"/>
-        <v>20194.947573991249</v>
+        <v>23608.468005511895</v>
       </c>
       <c r="BN30" s="13">
         <f t="shared" si="13"/>
-        <v>22214.442331390375</v>
+        <v>25969.314806063088</v>
       </c>
       <c r="BO30" s="13">
         <f t="shared" si="13"/>
-        <v>24435.886564529414</v>
+        <v>28566.2462866694</v>
       </c>
       <c r="BP30" s="13">
         <f t="shared" si="13"/>
-        <v>26879.475220982356</v>
+        <v>31422.870915336342</v>
       </c>
       <c r="BQ30" s="13">
         <f t="shared" si="13"/>
-        <v>29567.422743080595</v>
+        <v>34565.158006869977</v>
       </c>
       <c r="BR30" s="13">
         <f t="shared" si="13"/>
-        <v>32524.165017388656</v>
+        <v>38021.673807556981</v>
       </c>
       <c r="BS30" s="13">
         <f t="shared" si="13"/>
-        <v>35776.581519127525</v>
+        <v>41823.841188312683</v>
       </c>
       <c r="BT30" s="13">
         <f t="shared" si="13"/>
-        <v>39354.239671040283</v>
+        <v>46006.225307143955</v>
       </c>
       <c r="BU30" s="13">
         <f t="shared" si="13"/>
-        <v>43289.663638144317</v>
+        <v>50606.847837858353</v>
       </c>
       <c r="BV30" s="13">
         <f t="shared" si="13"/>
-        <v>47618.630001958751</v>
+        <v>55667.53262164419</v>
       </c>
       <c r="BW30" s="13">
         <f t="shared" si="13"/>
-        <v>52380.493002154632</v>
+        <v>61234.28588380861</v>
       </c>
       <c r="BX30" s="13">
         <f t="shared" si="13"/>
-        <v>57618.542302370101</v>
+        <v>67357.714472189473</v>
       </c>
       <c r="BY30" s="13">
         <f t="shared" si="13"/>
-        <v>63380.396532607119</v>
+        <v>74093.485919408427</v>
       </c>
       <c r="BZ30" s="13">
         <f t="shared" si="13"/>
-        <v>69718.436185867831</v>
+        <v>81502.834511349283</v>
       </c>
       <c r="CA30" s="13">
         <f t="shared" si="13"/>
-        <v>76690.279804454622</v>
+        <v>89653.117962484219</v>
       </c>
       <c r="CB30" s="13">
         <f t="shared" si="13"/>
-        <v>84359.307784900084</v>
+        <v>98618.429758732644</v>
       </c>
       <c r="CC30" s="13">
         <f t="shared" si="13"/>
-        <v>92795.238563390099</v>
+        <v>108480.27273460591</v>
       </c>
       <c r="CD30" s="13">
         <f t="shared" si="13"/>
-        <v>102074.76241972912</v>
+        <v>119328.30000806651</v>
       </c>
       <c r="CE30" s="13">
         <f t="shared" si="13"/>
-        <v>112282.23866170204</v>
+        <v>131261.13000887318</v>
       </c>
       <c r="CF30" s="13">
         <f t="shared" si="13"/>
-        <v>123510.46252787225</v>
+        <v>144387.24300976051</v>
       </c>
       <c r="CG30" s="13">
         <f t="shared" si="13"/>
-        <v>135861.5087806595</v>
+        <v>158825.96731073657</v>
       </c>
       <c r="CH30" s="13">
         <f t="shared" si="13"/>
-        <v>149447.65965872546</v>
+        <v>174708.56404181023</v>
       </c>
       <c r="CI30" s="13">
         <f t="shared" si="13"/>
-        <v>164392.42562459802</v>
+        <v>192179.42044599127</v>
       </c>
       <c r="CJ30" s="13">
         <f t="shared" si="13"/>
-        <v>180831.66818705783</v>
+        <v>211397.36249059043</v>
       </c>
       <c r="CK30" s="13">
         <f t="shared" si="13"/>
-        <v>198914.83500576363</v>
+        <v>232537.09873964949</v>
       </c>
       <c r="CL30" s="13">
         <f t="shared" si="13"/>
-        <v>218806.31850634</v>
+        <v>255790.80861361447</v>
       </c>
       <c r="CM30" s="13">
         <f t="shared" si="13"/>
-        <v>240686.95035697403</v>
+        <v>281369.88947497593</v>
       </c>
       <c r="CN30" s="13">
         <f t="shared" si="13"/>
-        <v>264755.64539267146</v>
+        <v>309506.87842247356</v>
       </c>
       <c r="CO30" s="13">
         <f t="shared" si="13"/>
-        <v>291231.20993193862</v>
+        <v>340457.56626472092</v>
       </c>
       <c r="CP30" s="13">
         <f t="shared" si="13"/>
-        <v>320354.3309251325</v>
+        <v>374503.32289119303</v>
       </c>
       <c r="CQ30" s="13">
         <f t="shared" si="13"/>
-        <v>352389.76401764579</v>
+        <v>411953.65518031234</v>
       </c>
       <c r="CR30" s="13">
         <f t="shared" si="13"/>
-        <v>387628.7404194104</v>
+        <v>453149.02069834364</v>
       </c>
       <c r="CS30" s="13">
         <f t="shared" si="13"/>
-        <v>426391.61446135148</v>
+        <v>498463.92276817805</v>
       </c>
       <c r="CT30" s="13">
         <f t="shared" si="13"/>
-        <v>469030.77590748668</v>
+        <v>548310.31504499586</v>
       </c>
       <c r="CU30" s="13">
         <f t="shared" si="13"/>
-        <v>515933.8534982354</v>
+        <v>603141.34654949547</v>
       </c>
       <c r="CV30" s="13">
         <f t="shared" si="13"/>
-        <v>567527.23884805897</v>
+        <v>663455.48120444512</v>
       </c>
       <c r="CW30" s="13">
         <f t="shared" si="13"/>
-        <v>624279.96273286489</v>
+        <v>729801.02932488965</v>
       </c>
       <c r="CX30" s="13">
         <f t="shared" si="13"/>
-        <v>686707.95900615142</v>
+        <v>802781.13225737866</v>
       </c>
       <c r="CY30" s="13">
         <f t="shared" si="13"/>
-        <v>755378.75490676658</v>
+        <v>883059.2454831166</v>
       </c>
       <c r="CZ30" s="13">
         <f t="shared" si="13"/>
-        <v>830916.63039744331</v>
+        <v>971365.17003142834</v>
       </c>
       <c r="DA30" s="13">
         <f t="shared" si="13"/>
-        <v>914008.29343718768</v>
+        <v>1068501.6870345713</v>
       </c>
       <c r="DB30" s="13">
         <f t="shared" si="13"/>
-        <v>1005409.1227809065</v>
+        <v>1175351.8557380287</v>
       </c>
       <c r="DC30" s="13">
         <f t="shared" si="13"/>
-        <v>1105950.0350589973</v>
+        <v>1292887.0413118317</v>
       </c>
       <c r="DD30" s="13">
         <f t="shared" si="13"/>
-        <v>1216545.0385648971</v>
+        <v>1422175.7454430149</v>
       </c>
       <c r="DE30" s="13">
         <f t="shared" si="13"/>
-        <v>1338199.542421387</v>
+        <v>1564393.3199873166</v>
       </c>
       <c r="DF30" s="13">
         <f t="shared" si="13"/>
-        <v>1472019.4966635259</v>
+        <v>1720832.6519860483</v>
       </c>
     </row>
     <row r="31" spans="2:110" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4021,6 +4035,9 @@
       <c r="V31" s="10">
         <v>43.593000000000004</v>
       </c>
+      <c r="W31" s="10">
+        <v>49.253999999999998</v>
+      </c>
       <c r="AD31" s="10">
         <v>0.14299999999999999</v>
       </c>
@@ -4043,43 +4060,43 @@
       </c>
       <c r="AJ31" s="10">
         <f t="shared" ref="AJ31:AS31" si="14">+AJ30-AJ32</f>
-        <v>74.112824999999987</v>
+        <v>86.640000000000015</v>
       </c>
       <c r="AK31" s="10">
         <f t="shared" si="14"/>
-        <v>140.8143675</v>
+        <v>164.61600000000004</v>
       </c>
       <c r="AL31" s="10">
         <f t="shared" si="14"/>
-        <v>267.54729824999993</v>
+        <v>312.7704</v>
       </c>
       <c r="AM31" s="10">
         <f t="shared" si="14"/>
-        <v>508.33986667499994</v>
+        <v>594.26376000000005</v>
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="14"/>
-        <v>559.17385334250002</v>
+        <v>653.69013599999994</v>
       </c>
       <c r="AO31" s="10">
         <f t="shared" si="14"/>
-        <v>615.09123867674998</v>
+        <v>719.05914960000018</v>
       </c>
       <c r="AP31" s="10">
         <f t="shared" si="14"/>
-        <v>676.60036254442502</v>
+        <v>790.9650645600002</v>
       </c>
       <c r="AQ31" s="10">
         <f t="shared" si="14"/>
-        <v>744.26039879886753</v>
+        <v>870.06157101600047</v>
       </c>
       <c r="AR31" s="10">
         <f t="shared" si="14"/>
-        <v>818.68643867875448</v>
+        <v>957.06772811760038</v>
       </c>
       <c r="AS31" s="10">
         <f t="shared" si="14"/>
-        <v>900.55508254662982</v>
+        <v>1052.7745009293608</v>
       </c>
     </row>
     <row r="32" spans="2:110" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4138,21 +4155,25 @@
         <f>+R30-R31</f>
         <v>6.6650000000000009</v>
       </c>
-      <c r="S32" s="24">
+      <c r="S32" s="11">
         <f>+S30-S31</f>
         <v>3.2514999999999992</v>
       </c>
-      <c r="T32" s="25">
+      <c r="T32" s="10">
         <f>+T30-T31</f>
         <v>12.372999999999999</v>
       </c>
-      <c r="U32" s="25">
+      <c r="U32" s="10">
         <f>+U30-U31</f>
         <v>18.613</v>
       </c>
-      <c r="V32" s="25">
+      <c r="V32" s="10">
         <f>+V30-V31</f>
         <v>18.296999999999997</v>
+      </c>
+      <c r="W32" s="10">
+        <f>+W30-W31</f>
+        <v>15.446000000000005</v>
       </c>
       <c r="AD32" s="10">
         <f>+AD30-AD31</f>
@@ -4180,43 +4201,43 @@
       </c>
       <c r="AJ32" s="10">
         <f t="shared" ref="AJ32:AS32" si="16">+AJ30*0.7</f>
-        <v>172.92992499999997</v>
+        <v>202.16</v>
       </c>
       <c r="AK32" s="10">
         <f t="shared" si="16"/>
-        <v>328.56685749999991</v>
+        <v>384.10399999999998</v>
       </c>
       <c r="AL32" s="10">
         <f t="shared" si="16"/>
-        <v>624.27702924999983</v>
+        <v>729.79759999999999</v>
       </c>
       <c r="AM32" s="10">
         <f t="shared" si="16"/>
-        <v>1186.1263555749995</v>
+        <v>1386.6154399999998</v>
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="16"/>
-        <v>1304.7389911324995</v>
+        <v>1525.2769839999999</v>
       </c>
       <c r="AO32" s="10">
         <f t="shared" si="16"/>
-        <v>1435.2128902457498</v>
+        <v>1677.8046823999998</v>
       </c>
       <c r="AP32" s="10">
         <f t="shared" si="16"/>
-        <v>1578.7341792703251</v>
+        <v>1845.5851506400002</v>
       </c>
       <c r="AQ32" s="10">
         <f t="shared" si="16"/>
-        <v>1736.6075971973576</v>
+        <v>2030.1436657040003</v>
       </c>
       <c r="AR32" s="10">
         <f t="shared" si="16"/>
-        <v>1910.2683569170933</v>
+        <v>2233.1580322744007</v>
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>2101.2951926088031</v>
+        <v>2456.4738355018408</v>
       </c>
     </row>
     <row r="33" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4277,6 +4298,9 @@
       <c r="V33" s="10">
         <v>96.094999999999999</v>
       </c>
+      <c r="W33" s="10">
+        <v>125.74</v>
+      </c>
       <c r="AD33" s="10">
         <v>10.157</v>
       </c>
@@ -4396,6 +4420,9 @@
       <c r="V34" s="10">
         <v>19.518999999999998</v>
       </c>
+      <c r="W34" s="10">
+        <v>29.436</v>
+      </c>
       <c r="AD34" s="10">
         <v>0.48599999999999999</v>
       </c>
@@ -4514,6 +4541,9 @@
       </c>
       <c r="V35" s="10">
         <v>90.668999999999997</v>
+      </c>
+      <c r="W35" s="10">
+        <v>88.616</v>
       </c>
       <c r="AD35" s="10">
         <v>3.5470000000000002</v>
@@ -4637,7 +4667,7 @@
         <v>72.369</v>
       </c>
       <c r="T36" s="11">
-        <f t="shared" ref="T36:V36" si="25">SUM(T33:T35)</f>
+        <f t="shared" ref="T36:W36" si="25">SUM(T33:T35)</f>
         <v>162.34299999999999</v>
       </c>
       <c r="U36" s="11">
@@ -4648,7 +4678,10 @@
         <f t="shared" si="25"/>
         <v>206.28300000000002</v>
       </c>
-      <c r="W36" s="11"/>
+      <c r="W36" s="11">
+        <f t="shared" si="25"/>
+        <v>243.79199999999997</v>
+      </c>
       <c r="X36" s="11"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -4781,7 +4814,7 @@
         <v>-69.117500000000007</v>
       </c>
       <c r="T37" s="11">
-        <f t="shared" ref="T37:V37" si="43">+T32-T36</f>
+        <f t="shared" ref="T37:W37" si="43">+T32-T36</f>
         <v>-149.97</v>
       </c>
       <c r="U37" s="11">
@@ -4792,7 +4825,10 @@
         <f t="shared" si="43"/>
         <v>-187.98600000000002</v>
       </c>
-      <c r="W37" s="11"/>
+      <c r="W37" s="11">
+        <f t="shared" si="43"/>
+        <v>-228.34599999999998</v>
+      </c>
       <c r="X37" s="11"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -4825,43 +4861,43 @@
       </c>
       <c r="AJ37" s="11">
         <f t="shared" ref="AJ37" si="47">+AJ32-AJ36</f>
-        <v>-88.964540000000056</v>
+        <v>-59.734465000000029</v>
       </c>
       <c r="AK37" s="11">
         <f t="shared" ref="AK37" si="48">+AK32-AK36</f>
-        <v>53.577669249999872</v>
+        <v>109.11481174999994</v>
       </c>
       <c r="AL37" s="11">
         <f t="shared" ref="AL37" si="49">+AL32-AL36</f>
-        <v>335.53838158749977</v>
+        <v>441.05895233749993</v>
       </c>
       <c r="AM37" s="11">
         <f t="shared" ref="AM37" si="50">+AM32-AM36</f>
-        <v>882.95077552937437</v>
+        <v>1083.4398599543747</v>
       </c>
       <c r="AN37" s="11">
         <f t="shared" ref="AN37" si="51">+AN32-AN36</f>
-        <v>986.404632084593</v>
+        <v>1206.9426249520934</v>
       </c>
       <c r="AO37" s="11">
         <f t="shared" ref="AO37" si="52">+AO32-AO36</f>
-        <v>1100.9618132454482</v>
+        <v>1343.5536053996982</v>
       </c>
       <c r="AP37" s="11">
         <f t="shared" ref="AP37" si="53">+AP32-AP36</f>
-        <v>1227.7705484200083</v>
+        <v>1494.6215197896834</v>
       </c>
       <c r="AQ37" s="11">
         <f t="shared" ref="AQ37" si="54">+AQ32-AQ36</f>
-        <v>1368.095784804525</v>
+        <v>1661.6318533111676</v>
       </c>
       <c r="AR37" s="11">
         <f t="shared" ref="AR37" si="55">+AR32-AR36</f>
-        <v>1523.330953904619</v>
+        <v>1846.2206292619264</v>
       </c>
       <c r="AS37" s="11">
         <f t="shared" ref="AS37" si="56">+AS32-AS36</f>
-        <v>1695.010919445705</v>
+        <v>2050.1895623387427</v>
       </c>
     </row>
     <row r="38" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4924,6 +4960,9 @@
       <c r="V38" s="10">
         <v>29.257999999999999</v>
       </c>
+      <c r="W38" s="10">
+        <v>28.234000000000002</v>
+      </c>
       <c r="AH38" s="10">
         <f t="shared" ref="AH38" si="57">SUM(O38:R38)</f>
         <v>18.153000000000002</v>
@@ -4974,7 +5013,7 @@
         <v>-41.103999999999992</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" ref="Q39:V39" si="61">+Q37+Q38</f>
+        <f t="shared" ref="Q39:W39" si="61">+Q37+Q38</f>
         <v>-43.721999999999994</v>
       </c>
       <c r="R39" s="11">
@@ -4997,7 +5036,10 @@
         <f t="shared" si="61"/>
         <v>-158.72800000000001</v>
       </c>
-      <c r="W39" s="11"/>
+      <c r="W39" s="11">
+        <f t="shared" si="61"/>
+        <v>-200.11199999999997</v>
+      </c>
       <c r="X39" s="11"/>
       <c r="Y39" s="11"/>
       <c r="Z39" s="11"/>
@@ -5030,43 +5072,43 @@
       </c>
       <c r="AJ39" s="11">
         <f t="shared" ref="AJ39" si="64">+AJ37+AJ38</f>
-        <v>-88.964540000000056</v>
+        <v>-59.734465000000029</v>
       </c>
       <c r="AK39" s="11">
         <f t="shared" ref="AK39" si="65">+AK37+AK38</f>
-        <v>53.577669249999872</v>
+        <v>109.11481174999994</v>
       </c>
       <c r="AL39" s="11">
         <f t="shared" ref="AL39" si="66">+AL37+AL38</f>
-        <v>335.53838158749977</v>
+        <v>441.05895233749993</v>
       </c>
       <c r="AM39" s="11">
         <f t="shared" ref="AM39" si="67">+AM37+AM38</f>
-        <v>882.95077552937437</v>
+        <v>1083.4398599543747</v>
       </c>
       <c r="AN39" s="11">
         <f t="shared" ref="AN39" si="68">+AN37+AN38</f>
-        <v>986.404632084593</v>
+        <v>1206.9426249520934</v>
       </c>
       <c r="AO39" s="11">
         <f t="shared" ref="AO39" si="69">+AO37+AO38</f>
-        <v>1100.9618132454482</v>
+        <v>1343.5536053996982</v>
       </c>
       <c r="AP39" s="11">
         <f t="shared" ref="AP39" si="70">+AP37+AP38</f>
-        <v>1227.7705484200083</v>
+        <v>1494.6215197896834</v>
       </c>
       <c r="AQ39" s="11">
         <f t="shared" ref="AQ39" si="71">+AQ37+AQ38</f>
-        <v>1368.095784804525</v>
+        <v>1661.6318533111676</v>
       </c>
       <c r="AR39" s="11">
         <f t="shared" ref="AR39" si="72">+AR37+AR38</f>
-        <v>1523.330953904619</v>
+        <v>1846.2206292619264</v>
       </c>
       <c r="AS39" s="11">
         <f t="shared" ref="AS39" si="73">+AS37+AS38</f>
-        <v>1695.010919445705</v>
+        <v>2050.1895623387427</v>
       </c>
     </row>
     <row r="40" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -5125,41 +5167,44 @@
       <c r="V40" s="10">
         <v>0</v>
       </c>
+      <c r="W40" s="10">
+        <v>0</v>
+      </c>
       <c r="AH40" s="10">
         <f t="shared" ref="AH40" si="74">SUM(O40:R40)</f>
         <v>0</v>
       </c>
       <c r="AL40" s="10">
         <f>+AL39*0.1</f>
-        <v>33.553838158749976</v>
+        <v>44.105895233749997</v>
       </c>
       <c r="AM40" s="10">
         <f t="shared" ref="AM40:AS40" si="75">+AM39*0.1</f>
-        <v>88.295077552937443</v>
+        <v>108.34398599543748</v>
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="75"/>
-        <v>98.640463208459309</v>
+        <v>120.69426249520934</v>
       </c>
       <c r="AO40" s="10">
         <f t="shared" si="75"/>
-        <v>110.09618132454483</v>
+        <v>134.35536053996984</v>
       </c>
       <c r="AP40" s="10">
         <f t="shared" si="75"/>
-        <v>122.77705484200084</v>
+        <v>149.46215197896834</v>
       </c>
       <c r="AQ40" s="10">
         <f t="shared" si="75"/>
-        <v>136.8095784804525</v>
+        <v>166.16318533111678</v>
       </c>
       <c r="AR40" s="10">
         <f t="shared" si="75"/>
-        <v>152.33309539046192</v>
+        <v>184.62206292619265</v>
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="75"/>
-        <v>169.5010919445705</v>
+        <v>205.01895623387429</v>
       </c>
     </row>
     <row r="41" spans="2:82" x14ac:dyDescent="0.25">
@@ -5191,7 +5236,7 @@
         <v>-25.897999999999996</v>
       </c>
       <c r="M41" s="11">
-        <f t="shared" ref="M41:V41" si="78">+M39-M40</f>
+        <f t="shared" ref="M41:W41" si="78">+M39-M40</f>
         <v>-34.438000000000002</v>
       </c>
       <c r="N41" s="11">
@@ -5230,7 +5275,10 @@
         <f t="shared" si="78"/>
         <v>-158.72800000000001</v>
       </c>
-      <c r="W41" s="11"/>
+      <c r="W41" s="11">
+        <f t="shared" si="78"/>
+        <v>-200.11199999999997</v>
+      </c>
       <c r="X41" s="11"/>
       <c r="Y41" s="11"/>
       <c r="Z41" s="11"/>
@@ -5263,191 +5311,191 @@
       </c>
       <c r="AJ41" s="11">
         <f t="shared" ref="AJ41" si="81">+AJ39-AJ40</f>
-        <v>-88.964540000000056</v>
+        <v>-59.734465000000029</v>
       </c>
       <c r="AK41" s="11">
         <f t="shared" ref="AK41" si="82">+AK39-AK40</f>
-        <v>53.577669249999872</v>
+        <v>109.11481174999994</v>
       </c>
       <c r="AL41" s="11">
         <f t="shared" ref="AL41" si="83">+AL39-AL40</f>
-        <v>301.98454342874982</v>
+        <v>396.95305710374993</v>
       </c>
       <c r="AM41" s="11">
         <f t="shared" ref="AM41" si="84">+AM39-AM40</f>
-        <v>794.65569797643695</v>
+        <v>975.0958739589372</v>
       </c>
       <c r="AN41" s="11">
         <f t="shared" ref="AN41" si="85">+AN39-AN40</f>
-        <v>887.76416887613368</v>
+        <v>1086.248362456884</v>
       </c>
       <c r="AO41" s="11">
         <f t="shared" ref="AO41" si="86">+AO39-AO40</f>
-        <v>990.8656319209033</v>
+        <v>1209.1982448597284</v>
       </c>
       <c r="AP41" s="11">
         <f t="shared" ref="AP41" si="87">+AP39-AP40</f>
-        <v>1104.9934935780075</v>
+        <v>1345.1593678107151</v>
       </c>
       <c r="AQ41" s="11">
         <f t="shared" ref="AQ41" si="88">+AQ39-AQ40</f>
-        <v>1231.2862063240725</v>
+        <v>1495.4686679800507</v>
       </c>
       <c r="AR41" s="11">
         <f t="shared" ref="AR41" si="89">+AR39-AR40</f>
-        <v>1370.9978585141571</v>
+        <v>1661.5985663357337</v>
       </c>
       <c r="AS41" s="11">
         <f t="shared" ref="AS41" si="90">+AS39-AS40</f>
-        <v>1525.5098275011344</v>
+        <v>1845.1706061048685</v>
       </c>
       <c r="AT41" s="11">
         <f>+AS41*(1+$AT$48)</f>
-        <v>1510.2547292261231</v>
+        <v>1826.7189000438198</v>
       </c>
       <c r="AU41" s="11">
         <f t="shared" ref="AU41:CD41" si="91">+AT41*(1+$AT$48)</f>
-        <v>1495.1521819338618</v>
+        <v>1808.4517110433815</v>
       </c>
       <c r="AV41" s="11">
         <f t="shared" si="91"/>
-        <v>1480.2006601145231</v>
+        <v>1790.3671939329477</v>
       </c>
       <c r="AW41" s="11">
         <f t="shared" si="91"/>
-        <v>1465.3986535133779</v>
+        <v>1772.4635219936181</v>
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="91"/>
-        <v>1450.7446669782441</v>
+        <v>1754.738886773682</v>
       </c>
       <c r="AY41" s="11">
         <f t="shared" si="91"/>
-        <v>1436.2372203084617</v>
+        <v>1737.1914979059452</v>
       </c>
       <c r="AZ41" s="11">
         <f t="shared" si="91"/>
-        <v>1421.8748481053772</v>
+        <v>1719.8195829268857</v>
       </c>
       <c r="BA41" s="11">
         <f t="shared" si="91"/>
-        <v>1407.6560996243234</v>
+        <v>1702.6213870976169</v>
       </c>
       <c r="BB41" s="11">
         <f t="shared" si="91"/>
-        <v>1393.5795386280802</v>
+        <v>1685.5951732266408</v>
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="91"/>
-        <v>1379.6437432417993</v>
+        <v>1668.7392214943743</v>
       </c>
       <c r="BD41" s="11">
         <f t="shared" si="91"/>
-        <v>1365.8473058093812</v>
+        <v>1652.0518292794306</v>
       </c>
       <c r="BE41" s="11">
         <f t="shared" si="91"/>
-        <v>1352.1888327512872</v>
+        <v>1635.5313109866363</v>
       </c>
       <c r="BF41" s="11">
         <f t="shared" si="91"/>
-        <v>1338.6669444237743</v>
+        <v>1619.17599787677</v>
       </c>
       <c r="BG41" s="11">
         <f t="shared" si="91"/>
-        <v>1325.2802749795367</v>
+        <v>1602.9842378980022</v>
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="91"/>
-        <v>1312.0274722297413</v>
+        <v>1586.9543955190222</v>
       </c>
       <c r="BI41" s="11">
         <f t="shared" si="91"/>
-        <v>1298.9071975074439</v>
+        <v>1571.084851563832</v>
       </c>
       <c r="BJ41" s="11">
         <f t="shared" si="91"/>
-        <v>1285.9181255323695</v>
+        <v>1555.3740030481936</v>
       </c>
       <c r="BK41" s="11">
         <f t="shared" si="91"/>
-        <v>1273.0589442770458</v>
+        <v>1539.8202630177116</v>
       </c>
       <c r="BL41" s="11">
         <f t="shared" si="91"/>
-        <v>1260.3283548342754</v>
+        <v>1524.4220603875344</v>
       </c>
       <c r="BM41" s="11">
         <f t="shared" si="91"/>
-        <v>1247.7250712859327</v>
+        <v>1509.177839783659</v>
       </c>
       <c r="BN41" s="11">
         <f t="shared" si="91"/>
-        <v>1235.2478205730733</v>
+        <v>1494.0860613858224</v>
       </c>
       <c r="BO41" s="11">
         <f t="shared" si="91"/>
-        <v>1222.8953423673427</v>
+        <v>1479.1452007719643</v>
       </c>
       <c r="BP41" s="11">
         <f t="shared" si="91"/>
-        <v>1210.6663889436693</v>
+        <v>1464.3537487642445</v>
       </c>
       <c r="BQ41" s="11">
         <f t="shared" si="91"/>
-        <v>1198.5597250542326</v>
+        <v>1449.710211276602</v>
       </c>
       <c r="BR41" s="11">
         <f t="shared" si="91"/>
-        <v>1186.5741278036903</v>
+        <v>1435.213109163836</v>
       </c>
       <c r="BS41" s="11">
         <f t="shared" si="91"/>
-        <v>1174.7083865256534</v>
+        <v>1420.8609780721977</v>
       </c>
       <c r="BT41" s="11">
         <f t="shared" si="91"/>
-        <v>1162.9613026603968</v>
+        <v>1406.6523682914756</v>
       </c>
       <c r="BU41" s="11">
         <f t="shared" si="91"/>
-        <v>1151.3316896337928</v>
+        <v>1392.5858446085608</v>
       </c>
       <c r="BV41" s="11">
         <f t="shared" si="91"/>
-        <v>1139.8183727374549</v>
+        <v>1378.6599861624752</v>
       </c>
       <c r="BW41" s="11">
         <f t="shared" si="91"/>
-        <v>1128.4201890100803</v>
+        <v>1364.8733863008504</v>
       </c>
       <c r="BX41" s="11">
         <f t="shared" si="91"/>
-        <v>1117.1359871199795</v>
+        <v>1351.2246524378418</v>
       </c>
       <c r="BY41" s="11">
         <f t="shared" si="91"/>
-        <v>1105.9646272487796</v>
+        <v>1337.7124059134633</v>
       </c>
       <c r="BZ41" s="11">
         <f t="shared" si="91"/>
-        <v>1094.9049809762919</v>
+        <v>1324.3352818543285</v>
       </c>
       <c r="CA41" s="11">
         <f t="shared" si="91"/>
-        <v>1083.9559311665289</v>
+        <v>1311.0919290357851</v>
       </c>
       <c r="CB41" s="11">
         <f t="shared" si="91"/>
-        <v>1073.1163718548637</v>
+        <v>1297.9810097454272</v>
       </c>
       <c r="CC41" s="11">
         <f t="shared" si="91"/>
-        <v>1062.385208136315</v>
+        <v>1285.001199647973</v>
       </c>
       <c r="CD41" s="11">
         <f t="shared" si="91"/>
-        <v>1051.7613560549519</v>
+        <v>1272.1511876514933</v>
       </c>
     </row>
     <row r="42" spans="2:82" x14ac:dyDescent="0.25">
@@ -5472,7 +5520,7 @@
         <v>-9.4799827338986162E-2</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" ref="K42:V42" si="93">+K41/K43</f>
+        <f t="shared" ref="K42:W42" si="93">+K41/K43</f>
         <v>-0.10986800423191202</v>
       </c>
       <c r="L42" s="12">
@@ -5519,7 +5567,10 @@
         <f t="shared" si="93"/>
         <v>-0.43017709678955141</v>
       </c>
-      <c r="W42" s="12"/>
+      <c r="W42" s="12">
+        <f t="shared" si="93"/>
+        <v>-0.53905375087716234</v>
+      </c>
       <c r="X42" s="12"/>
       <c r="Y42" s="12"/>
       <c r="Z42" s="12"/>
@@ -5547,43 +5598,43 @@
       </c>
       <c r="AJ42" s="1">
         <f t="shared" ref="AJ42:AS42" si="95">AJ41/AJ43</f>
-        <v>-0.41764968185565243</v>
+        <v>-0.28042723879725112</v>
       </c>
       <c r="AK42" s="1">
         <f t="shared" si="95"/>
-        <v>0.25152377022159395</v>
+        <v>0.5122464120325565</v>
       </c>
       <c r="AL42" s="1">
         <f t="shared" si="95"/>
-        <v>1.4176856137101561</v>
+        <v>1.8635213312069021</v>
       </c>
       <c r="AM42" s="1">
         <f t="shared" si="95"/>
-        <v>3.7305616310120877</v>
+        <v>4.5776494942559047</v>
       </c>
       <c r="AN42" s="1">
         <f t="shared" si="95"/>
-        <v>4.1676652595962915</v>
+        <v>5.099461909164491</v>
       </c>
       <c r="AO42" s="1">
         <f t="shared" si="95"/>
-        <v>4.6516816243130688</v>
+        <v>5.6766579388380878</v>
       </c>
       <c r="AP42" s="1">
         <f t="shared" si="95"/>
-        <v>5.18746211743938</v>
+        <v>6.3149360634169005</v>
       </c>
       <c r="AQ42" s="1">
         <f t="shared" si="95"/>
-        <v>5.7803512764130716</v>
+        <v>7.0205726169883427</v>
       </c>
       <c r="AR42" s="1">
         <f t="shared" si="95"/>
-        <v>6.4362364986456191</v>
+        <v>7.8004799732784198</v>
       </c>
       <c r="AS42" s="1">
         <f t="shared" si="95"/>
-        <v>7.1616027478309849</v>
+        <v>8.662270569927065</v>
       </c>
     </row>
     <row r="43" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -5641,6 +5692,9 @@
       </c>
       <c r="V43" s="10">
         <v>368.98291699999999</v>
+      </c>
+      <c r="W43" s="10">
+        <v>371.22828600000003</v>
       </c>
       <c r="AD43" s="10">
         <v>115.045097</v>
@@ -5789,7 +5843,7 @@
         <v>0.48198493285293165</v>
       </c>
       <c r="O46" s="16">
-        <f t="shared" ref="O46:V46" si="102">+O32/O30</f>
+        <f t="shared" ref="O46:W46" si="102">+O32/O30</f>
         <v>0.54972302822474273</v>
       </c>
       <c r="P46" s="16">
@@ -5819,6 +5873,10 @@
       <c r="V46" s="16">
         <f t="shared" si="102"/>
         <v>0.29563742123121661</v>
+      </c>
+      <c r="W46" s="16">
+        <f t="shared" si="102"/>
+        <v>0.2387326120556415</v>
       </c>
       <c r="AF46" s="4"/>
       <c r="AG46" s="4"/>
@@ -5866,7 +5924,7 @@
       </c>
       <c r="AT49" s="4">
         <f>NPV(AT46,AI41:CD41)</f>
-        <v>4553.2127023355706</v>
+        <v>5641.3511085665414</v>
       </c>
     </row>
     <row r="50" spans="2:46" x14ac:dyDescent="0.25">
@@ -5875,7 +5933,7 @@
       </c>
       <c r="AT50" s="1">
         <f>AT49/Main!J3</f>
-        <v>12.33990109719787</v>
+        <v>15.205798136297956</v>
       </c>
     </row>
     <row r="51" spans="2:46" s="7" customFormat="1" x14ac:dyDescent="0.25">
